--- a/data/a_Eingangsdaten/Wärme/Raumwärmebedarf_täglich_23.xlsx
+++ b/data/a_Eingangsdaten/Wärme/Raumwärmebedarf_täglich_23.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="C2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1240.882917466411</v>
+        <v>1239.624092839704</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="D3" t="n">
-        <v>1483.354292143755</v>
+        <v>1470.25183104244</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="D4" t="n">
-        <v>2110.927261896883</v>
+        <v>2118.892344737634</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="C5" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="D5" t="n">
-        <v>1882.718909259382</v>
+        <v>1888.264606534898</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1697.299622741412</v>
+        <v>1686.465335607504</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1811.403799060163</v>
+        <v>1801.779204708873</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="C8" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="D8" t="n">
-        <v>1882.718909259382</v>
+        <v>1888.264606534898</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>2025.34912965782</v>
+        <v>2017.992709273937</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2139.45330597657</v>
+        <v>2147.720812012976</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2282.083526375008</v>
+        <v>2291.863148389686</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="D12" t="n">
-        <v>1996.823085578132</v>
+        <v>1989.164241998595</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="D13" t="n">
-        <v>1854.192865179694</v>
+        <v>1845.021905621885</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>1868.455887219538</v>
+        <v>1873.850372897227</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="C15" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1982.560063538288</v>
+        <v>1989.164241998595</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="D16" t="n">
-        <v>2139.45330597657</v>
+        <v>2147.720812012976</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>2438.97676881329</v>
+        <v>2450.419718404066</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>2709.974187570322</v>
+        <v>2738.704391157486</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="C19" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="D19" t="n">
-        <v>3023.760672446886</v>
+        <v>3041.403297548577</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="C20" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="D20" t="n">
-        <v>3066.549738566417</v>
+        <v>3070.231764823919</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         <v>21.5</v>
       </c>
       <c r="D21" t="n">
-        <v>3066.549738566417</v>
+        <v>3099.060232099261</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         <v>21.9</v>
       </c>
       <c r="D22" t="n">
-        <v>3123.601826725792</v>
+        <v>3156.717166649944</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="C23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="D23" t="n">
-        <v>2938.182540207823</v>
+        <v>2954.917895722551</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="D24" t="n">
-        <v>2852.60440796876</v>
+        <v>2854.018260258854</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C25" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="D25" t="n">
-        <v>2809.815341849229</v>
+        <v>2796.36132570817</v>
       </c>
     </row>
     <row r="26">
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="C26" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="D26" t="n">
-        <v>2952.445562247667</v>
+        <v>2954.917895722551</v>
       </c>
     </row>
     <row r="27">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="C27" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D27" t="n">
-        <v>3038.02369448673</v>
+        <v>3055.817531186247</v>
       </c>
     </row>
     <row r="28">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C28" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="D28" t="n">
-        <v>2881.130452048448</v>
+        <v>2897.260961171867</v>
       </c>
     </row>
     <row r="29">
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="C29" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D29" t="n">
-        <v>2980.971606327354</v>
+        <v>2998.160596635564</v>
       </c>
     </row>
     <row r="30">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="C30" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D30" t="n">
-        <v>3023.760672446886</v>
+        <v>3070.231764823919</v>
       </c>
     </row>
     <row r="31">
@@ -921,13 +921,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C31" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="D31" t="n">
-        <v>2610.133033291416</v>
+        <v>2652.21898933146</v>
       </c>
     </row>
     <row r="32">
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="C32" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="D32" t="n">
-        <v>2453.239790853133</v>
+        <v>2493.66241931708</v>
       </c>
     </row>
     <row r="33">
@@ -953,13 +953,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="C33" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="D33" t="n">
-        <v>2310.609570454696</v>
+        <v>2320.691615665028</v>
       </c>
     </row>
     <row r="34">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="C34" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="D34" t="n">
-        <v>2353.398636574227</v>
+        <v>2335.105849302699</v>
       </c>
     </row>
     <row r="35">
@@ -985,13 +985,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="C35" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="D35" t="n">
-        <v>2096.664239857039</v>
+        <v>2090.063877462292</v>
       </c>
     </row>
     <row r="36">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="C36" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="D36" t="n">
-        <v>2538.817923092196</v>
+        <v>2536.905120230093</v>
       </c>
     </row>
     <row r="37">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="C37" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="D37" t="n">
-        <v>2909.656496128135</v>
+        <v>2897.260961171867</v>
       </c>
     </row>
     <row r="38">
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="C38" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="D38" t="n">
-        <v>2980.971606327354</v>
+        <v>2954.917895722551</v>
       </c>
     </row>
     <row r="39">
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="C39" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="D39" t="n">
-        <v>3251.969025084386</v>
+        <v>3243.202568475971</v>
       </c>
     </row>
     <row r="40">
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="C40" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D40" t="n">
-        <v>3237.706003044543</v>
+        <v>3257.616802113641</v>
       </c>
     </row>
     <row r="41">
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="C41" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="D41" t="n">
-        <v>3152.12787080548</v>
+        <v>3214.374101200629</v>
       </c>
     </row>
     <row r="42">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="C42" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="D42" t="n">
-        <v>2809.815341849229</v>
+        <v>2897.260961171867</v>
       </c>
     </row>
     <row r="43">
@@ -1113,13 +1113,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="C43" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="D43" t="n">
-        <v>2381.924680653914</v>
+        <v>2464.833952041738</v>
       </c>
     </row>
     <row r="44">
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="C44" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="D44" t="n">
-        <v>2153.716328016414</v>
+        <v>2205.37774656366</v>
       </c>
     </row>
     <row r="45">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="D45" t="n">
-        <v>2282.083526375008</v>
+        <v>2349.52008294037</v>
       </c>
     </row>
     <row r="46">
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="C46" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="D46" t="n">
-        <v>2467.502812892978</v>
+        <v>2565.733587505435</v>
       </c>
     </row>
     <row r="47">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="C47" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="D47" t="n">
-        <v>2553.08094513204</v>
+        <v>2652.21898933146</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         <v>16</v>
       </c>
       <c r="D48" t="n">
-        <v>2282.083526375008</v>
+        <v>2306.277382027357</v>
       </c>
     </row>
     <row r="49">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="C49" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="D49" t="n">
-        <v>1611.72149050235</v>
+        <v>1599.979933781479</v>
       </c>
     </row>
     <row r="50">
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="D50" t="n">
-        <v>1668.773578661725</v>
+        <v>1628.808401056821</v>
       </c>
     </row>
     <row r="51">
@@ -1241,13 +1241,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="C51" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="D51" t="n">
-        <v>1982.560063538288</v>
+        <v>1931.507307447911</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         <v>12.9</v>
       </c>
       <c r="D52" t="n">
-        <v>1839.92984313985</v>
+        <v>1859.436139259557</v>
       </c>
     </row>
     <row r="53">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="C53" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="D53" t="n">
-        <v>1797.140777020319</v>
+        <v>1845.021905621885</v>
       </c>
     </row>
     <row r="54">
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C54" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="D54" t="n">
-        <v>1896.981931299226</v>
+        <v>1888.264606534898</v>
       </c>
     </row>
     <row r="55">
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="D55" t="n">
-        <v>1896.981931299226</v>
+        <v>1873.850372897227</v>
       </c>
     </row>
     <row r="56">
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="C56" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2225.031438215633</v>
+        <v>2190.963512925989</v>
       </c>
     </row>
     <row r="57">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="C57" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2667.185121450791</v>
+        <v>2666.633222969131</v>
       </c>
     </row>
     <row r="58">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="C58" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D58" t="n">
-        <v>3038.02369448673</v>
+        <v>3055.817531186247</v>
       </c>
     </row>
     <row r="59">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="C59" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="D59" t="n">
-        <v>3009.497650407042</v>
+        <v>3026.989063910906</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         <v>20.6</v>
       </c>
       <c r="D60" t="n">
-        <v>2938.182540207823</v>
+        <v>2969.332129360222</v>
       </c>
     </row>
     <row r="61">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C61" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="D61" t="n">
-        <v>2838.341385928916</v>
+        <v>2839.604026621183</v>
       </c>
     </row>
     <row r="62">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="C62" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="D62" t="n">
-        <v>2638.659077371103</v>
+        <v>2608.976288418447</v>
       </c>
     </row>
     <row r="63">
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="C63" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="D63" t="n">
-        <v>2695.711165530478</v>
+        <v>2681.047456606802</v>
       </c>
     </row>
     <row r="64">
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="C64" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="D64" t="n">
-        <v>2567.343967171884</v>
+        <v>2623.390522056118</v>
       </c>
     </row>
     <row r="65">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C65" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="D65" t="n">
-        <v>2638.659077371103</v>
+        <v>2652.21898933146</v>
       </c>
     </row>
     <row r="66">
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C66" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="D66" t="n">
-        <v>2695.711165530478</v>
+        <v>2709.875923882144</v>
       </c>
     </row>
     <row r="67">
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="C67" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="D67" t="n">
-        <v>2567.343967171884</v>
+        <v>2551.319353867763</v>
       </c>
     </row>
     <row r="68">
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="C68" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="D68" t="n">
-        <v>2553.08094513204</v>
+        <v>2508.07665295475</v>
       </c>
     </row>
     <row r="69">
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="C69" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="D69" t="n">
-        <v>2139.45330597657</v>
+        <v>2061.23541018695</v>
       </c>
     </row>
     <row r="70">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="C70" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="D70" t="n">
-        <v>2082.401217817195</v>
+        <v>2061.23541018695</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         <v>19.4</v>
       </c>
       <c r="D71" t="n">
-        <v>2767.026275729697</v>
+        <v>2796.36132570817</v>
       </c>
     </row>
     <row r="72">
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C72" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="D72" t="n">
-        <v>2481.765834932821</v>
+        <v>2479.248185679408</v>
       </c>
     </row>
     <row r="73">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="C73" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="D73" t="n">
-        <v>1369.250115825005</v>
+        <v>1354.937961941072</v>
       </c>
     </row>
     <row r="74">
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="C74" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="D74" t="n">
-        <v>1868.455887219538</v>
+        <v>1859.436139259557</v>
       </c>
     </row>
     <row r="75">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="C75" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="D75" t="n">
-        <v>2624.396055331259</v>
+        <v>2637.804755693789</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         <v>16.8</v>
       </c>
       <c r="D76" t="n">
-        <v>2396.187702693759</v>
+        <v>2421.591251128725</v>
       </c>
     </row>
     <row r="77">
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="D77" t="n">
-        <v>1697.299622741412</v>
+        <v>1700.879569245175</v>
       </c>
     </row>
     <row r="78">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="C78" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>1412.039181944536</v>
+        <v>1398.180662854085</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         <v>10.7</v>
       </c>
       <c r="D79" t="n">
-        <v>1526.143358263286</v>
+        <v>1542.322999230795</v>
       </c>
     </row>
     <row r="80">
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="C80" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="D80" t="n">
-        <v>1711.562644781256</v>
+        <v>1715.293802882847</v>
       </c>
     </row>
     <row r="81">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="C81" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="D81" t="n">
-        <v>1611.72149050235</v>
+        <v>1599.979933781479</v>
       </c>
     </row>
     <row r="82">
@@ -1737,13 +1737,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="C82" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D82" t="n">
-        <v>1340.724071745317</v>
+        <v>1340.523728303401</v>
       </c>
     </row>
     <row r="83">
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="C83" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D83" t="n">
-        <v>1226.619895426567</v>
+        <v>1196.381391926691</v>
       </c>
     </row>
     <row r="84">
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="C84" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D84" t="n">
-        <v>1340.724071745317</v>
+        <v>1326.10949466573</v>
       </c>
     </row>
     <row r="85">
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="C85" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="D85" t="n">
-        <v>1740.088688860943</v>
+        <v>1744.122270158189</v>
       </c>
     </row>
     <row r="86">
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="C86" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="D86" t="n">
-        <v>1954.034019458601</v>
+        <v>1945.921541085582</v>
       </c>
     </row>
     <row r="87">
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="C87" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="D87" t="n">
-        <v>2524.554901052353</v>
+        <v>2522.490886592421</v>
       </c>
     </row>
     <row r="88">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="C88" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="D88" t="n">
-        <v>2496.028856972665</v>
+        <v>2493.66241931708</v>
       </c>
     </row>
     <row r="89">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="C89" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="D89" t="n">
-        <v>1811.403799060163</v>
+        <v>1772.950737433531</v>
       </c>
     </row>
     <row r="90">
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="C90" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D90" t="n">
-        <v>1340.724071745317</v>
+        <v>1326.10949466573</v>
       </c>
     </row>
     <row r="91">
@@ -1881,13 +1881,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="C91" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="D91" t="n">
-        <v>1554.669402342974</v>
+        <v>1527.908765593124</v>
       </c>
     </row>
     <row r="92">
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="C92" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="D92" t="n">
-        <v>1811.403799060163</v>
+        <v>1787.364971071201</v>
       </c>
     </row>
     <row r="93">
@@ -1913,13 +1913,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="C93" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="D93" t="n">
-        <v>2210.768416175789</v>
+        <v>2176.549279288318</v>
       </c>
     </row>
     <row r="94">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="C94" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="D94" t="n">
-        <v>2581.606989211728</v>
+        <v>2565.733587505435</v>
       </c>
     </row>
     <row r="95">
@@ -1945,13 +1945,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="D95" t="n">
-        <v>2681.448143490635</v>
+        <v>2681.047456606802</v>
       </c>
     </row>
     <row r="96">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="C96" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="D96" t="n">
-        <v>2538.817923092196</v>
+        <v>2551.319353867763</v>
       </c>
     </row>
     <row r="97">
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="C97" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="D97" t="n">
-        <v>2239.294460255477</v>
+        <v>2219.791980201331</v>
       </c>
     </row>
     <row r="98">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="C98" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="D98" t="n">
-        <v>2082.401217817195</v>
+        <v>2046.821176549279</v>
       </c>
     </row>
     <row r="99">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="C99" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="D99" t="n">
-        <v>2068.138195777351</v>
+        <v>2061.23541018695</v>
       </c>
     </row>
     <row r="100">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="C100" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="D100" t="n">
-        <v>1939.770997418757</v>
+        <v>1902.678840172569</v>
       </c>
     </row>
     <row r="101">
@@ -2041,13 +2041,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="D101" t="n">
-        <v>1568.932424382818</v>
+        <v>1556.737232868466</v>
       </c>
     </row>
     <row r="102">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="C102" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="D102" t="n">
-        <v>1740.088688860943</v>
+        <v>1715.293802882847</v>
       </c>
     </row>
     <row r="103">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="C103" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="D103" t="n">
-        <v>1825.666821100006</v>
+        <v>1830.607671984214</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         <v>13.3</v>
       </c>
       <c r="D104" t="n">
-        <v>1896.981931299226</v>
+        <v>1917.09307381024</v>
       </c>
     </row>
     <row r="105">
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="C105" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="D105" t="n">
-        <v>1968.297041498445</v>
+        <v>1960.335774723253</v>
       </c>
     </row>
     <row r="106">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C106" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="D106" t="n">
-        <v>1896.981931299226</v>
+        <v>1888.264606534898</v>
       </c>
     </row>
     <row r="107">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="C107" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="D107" t="n">
-        <v>1782.877754980475</v>
+        <v>1758.53650379586</v>
       </c>
     </row>
     <row r="108">
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="C108" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="D108" t="n">
-        <v>1754.351710900788</v>
+        <v>1715.293802882847</v>
       </c>
     </row>
     <row r="109">
@@ -2169,13 +2169,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="C109" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="D109" t="n">
-        <v>1725.8256668211</v>
+        <v>1715.293802882847</v>
       </c>
     </row>
     <row r="110">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="C110" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="D110" t="n">
-        <v>1797.140777020319</v>
+        <v>1787.364971071201</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         <v>14</v>
       </c>
       <c r="D111" t="n">
-        <v>1996.823085578132</v>
+        <v>2017.992709273937</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="D112" t="n">
-        <v>1312.19802766563</v>
+        <v>1326.10949466573</v>
       </c>
     </row>
     <row r="113">
@@ -2233,13 +2233,13 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="C113" t="n">
-        <v>6.4</v>
+        <v>6.199999999999999</v>
       </c>
       <c r="D113" t="n">
-        <v>912.8334105500032</v>
+        <v>893.6824855356007</v>
       </c>
     </row>
     <row r="114">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="C114" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="D114" t="n">
-        <v>1083.989675028129</v>
+        <v>1066.653289187652</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         <v>10.6</v>
       </c>
       <c r="D115" t="n">
-        <v>1511.880336223443</v>
+        <v>1527.908765593124</v>
       </c>
     </row>
     <row r="116">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="C116" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="D116" t="n">
-        <v>1968.297041498445</v>
+        <v>1960.335774723253</v>
       </c>
     </row>
     <row r="117">
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="C117" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="D117" t="n">
-        <v>2053.875173737507</v>
+        <v>2046.821176549279</v>
       </c>
     </row>
     <row r="118">
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="C118" t="n">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="D118" t="n">
-        <v>1782.877754980475</v>
+        <v>1715.293802882847</v>
       </c>
     </row>
     <row r="119">
@@ -2329,13 +2329,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>1426.30220398438</v>
+        <v>1412.594896491756</v>
       </c>
     </row>
     <row r="120">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="C120" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D120" t="n">
-        <v>1326.461049705473</v>
+        <v>1311.695261028059</v>
       </c>
     </row>
     <row r="121">
@@ -2361,13 +2361,13 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C121" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="C121" t="n">
-        <v>10.2</v>
-      </c>
       <c r="D121" t="n">
-        <v>1454.828248064068</v>
+        <v>1412.594896491756</v>
       </c>
     </row>
     <row r="122">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>19.7</v>
+        <v>20.1</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="C271" t="n">
         <v>0</v>
@@ -4825,13 +4825,13 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="C275" t="n">
-        <v>5.300000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="D275" t="n">
-        <v>755.9401681117215</v>
+        <v>792.7828500719038</v>
       </c>
     </row>
     <row r="276">
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="C276" t="n">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="C278" t="n">
-        <v>7.699999999999999</v>
+        <v>7.800000000000001</v>
       </c>
       <c r="D278" t="n">
-        <v>1098.252697067973</v>
+        <v>1124.310223738336</v>
       </c>
     </row>
     <row r="279">
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="C279" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="D279" t="n">
-        <v>1169.567807267191</v>
+        <v>1210.795625564362</v>
       </c>
     </row>
     <row r="280">
@@ -4905,13 +4905,13 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="C280" t="n">
-        <v>7.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="D280" t="n">
-        <v>1041.200608908598</v>
+        <v>1095.481756462994</v>
       </c>
     </row>
     <row r="281">
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="C281" t="n">
-        <v>5.800000000000001</v>
+        <v>6.199999999999999</v>
       </c>
       <c r="D281" t="n">
-        <v>827.2552783109405</v>
+        <v>893.6824855356007</v>
       </c>
     </row>
     <row r="282">
@@ -4937,13 +4937,13 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="C282" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="D282" t="n">
-        <v>941.3594546296908</v>
+        <v>936.9251864486137</v>
       </c>
     </row>
     <row r="283">
@@ -4953,13 +4953,13 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="C283" t="n">
-        <v>6.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="D283" t="n">
-        <v>898.5703885101595</v>
+        <v>879.2682518979298</v>
       </c>
     </row>
     <row r="284">
@@ -5001,13 +5001,13 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="C286" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>713.1511019921901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
@@ -5033,13 +5033,13 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="C288" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="D288" t="n">
-        <v>1012.67456482891</v>
+        <v>994.5821209992976</v>
       </c>
     </row>
     <row r="289">
@@ -5049,13 +5049,13 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="C289" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="D289" t="n">
-        <v>1911.244953339069</v>
+        <v>1945.921541085582</v>
       </c>
     </row>
     <row r="290">
@@ -5065,13 +5065,13 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="C290" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="D290" t="n">
-        <v>2096.664239857039</v>
+        <v>2133.306578375305</v>
       </c>
     </row>
     <row r="291">
@@ -5081,13 +5081,13 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="C291" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="D291" t="n">
-        <v>2039.612151697664</v>
+        <v>2090.063877462292</v>
       </c>
     </row>
     <row r="292">
@@ -5103,7 +5103,7 @@
         <v>13.1</v>
       </c>
       <c r="D292" t="n">
-        <v>1868.455887219538</v>
+        <v>1888.264606534898</v>
       </c>
     </row>
     <row r="293">
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="C293" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D293" t="n">
-        <v>1383.513137864849</v>
+        <v>1326.10949466573</v>
       </c>
     </row>
     <row r="294">
@@ -5129,13 +5129,13 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>10.6</v>
+        <v>11.1</v>
       </c>
       <c r="C294" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="D294" t="n">
-        <v>1340.724071745317</v>
+        <v>1282.866793752717</v>
       </c>
     </row>
     <row r="295">
@@ -5145,13 +5145,13 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="C295" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="D295" t="n">
-        <v>1183.830829307035</v>
+        <v>1153.138691013678</v>
       </c>
     </row>
     <row r="296">
@@ -5167,7 +5167,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="D296" t="n">
-        <v>1326.461049705473</v>
+        <v>1340.523728303401</v>
       </c>
     </row>
     <row r="297">
@@ -5183,7 +5183,7 @@
         <v>10.2</v>
       </c>
       <c r="D297" t="n">
-        <v>1454.828248064068</v>
+        <v>1470.25183104244</v>
       </c>
     </row>
     <row r="298">
@@ -5199,7 +5199,7 @@
         <v>9.4</v>
       </c>
       <c r="D298" t="n">
-        <v>1340.724071745317</v>
+        <v>1354.937961941072</v>
       </c>
     </row>
     <row r="299">
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="C299" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D299" t="n">
-        <v>1440.565226024224</v>
+        <v>1441.423363767098</v>
       </c>
     </row>
     <row r="300">
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="C300" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D300" t="n">
-        <v>1440.565226024224</v>
+        <v>1441.423363767098</v>
       </c>
     </row>
     <row r="301">
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C301" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="D301" t="n">
-        <v>1568.932424382818</v>
+        <v>1556.737232868466</v>
       </c>
     </row>
     <row r="302">
@@ -5257,13 +5257,13 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="C302" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="D302" t="n">
-        <v>1483.354292143755</v>
+        <v>1455.837597404769</v>
       </c>
     </row>
     <row r="303">
@@ -5273,13 +5273,13 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="C303" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D303" t="n">
-        <v>1198.093851346879</v>
+        <v>1196.381391926691</v>
       </c>
     </row>
     <row r="304">
@@ -5289,13 +5289,13 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="C304" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="D304" t="n">
-        <v>1212.356873386723</v>
+        <v>1210.795625564362</v>
       </c>
     </row>
     <row r="305">
@@ -5305,13 +5305,13 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C305" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D305" t="n">
-        <v>1469.091270103912</v>
+        <v>1470.25183104244</v>
       </c>
     </row>
     <row r="306">
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="C306" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="D306" t="n">
-        <v>1454.828248064068</v>
+        <v>1441.423363767098</v>
       </c>
     </row>
     <row r="307">
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C307" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="D307" t="n">
-        <v>1540.406380303131</v>
+        <v>1542.322999230795</v>
       </c>
     </row>
     <row r="308">
@@ -5359,7 +5359,7 @@
         <v>12.8</v>
       </c>
       <c r="D308" t="n">
-        <v>1825.666821100006</v>
+        <v>1845.021905621885</v>
       </c>
     </row>
     <row r="309">
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="C309" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="D309" t="n">
-        <v>1839.92984313985</v>
+        <v>1830.607671984214</v>
       </c>
     </row>
     <row r="310">
@@ -5385,13 +5385,13 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C310" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="D310" t="n">
-        <v>1554.669402342974</v>
+        <v>1556.737232868466</v>
       </c>
     </row>
     <row r="311">
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C311" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="D311" t="n">
-        <v>1554.669402342974</v>
+        <v>1556.737232868466</v>
       </c>
     </row>
     <row r="312">
@@ -5423,7 +5423,7 @@
         <v>12.2</v>
       </c>
       <c r="D312" t="n">
-        <v>1740.088688860943</v>
+        <v>1758.53650379586</v>
       </c>
     </row>
     <row r="313">
@@ -5433,13 +5433,13 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="C313" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D313" t="n">
-        <v>1839.92984313985</v>
+        <v>1845.021905621885</v>
       </c>
     </row>
     <row r="314">
@@ -5455,7 +5455,7 @@
         <v>12.9</v>
       </c>
       <c r="D314" t="n">
-        <v>1839.92984313985</v>
+        <v>1859.436139259557</v>
       </c>
     </row>
     <row r="315">
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C315" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="D315" t="n">
-        <v>1925.507975378913</v>
+        <v>1917.09307381024</v>
       </c>
     </row>
     <row r="316">
@@ -5481,13 +5481,13 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="C316" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="D316" t="n">
-        <v>2125.190283936726</v>
+        <v>2133.306578375305</v>
       </c>
     </row>
     <row r="317">
@@ -5503,7 +5503,7 @@
         <v>15.4</v>
       </c>
       <c r="D317" t="n">
-        <v>2196.505394135946</v>
+        <v>2219.791980201331</v>
       </c>
     </row>
     <row r="318">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="C318" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="D318" t="n">
-        <v>1754.351710900788</v>
+        <v>1744.122270158189</v>
       </c>
     </row>
     <row r="319">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C319" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D319" t="n">
-        <v>1469.091270103912</v>
+        <v>1470.25183104244</v>
       </c>
     </row>
     <row r="320">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="C320" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="D320" t="n">
-        <v>1725.8256668211</v>
+        <v>1715.293802882847</v>
       </c>
     </row>
     <row r="321">
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="C321" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="D321" t="n">
-        <v>2025.34912965782</v>
+        <v>2017.992709273937</v>
       </c>
     </row>
     <row r="322">
@@ -5577,13 +5577,13 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="C322" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="D322" t="n">
-        <v>2310.609570454696</v>
+        <v>2306.277382027357</v>
       </c>
     </row>
     <row r="323">
@@ -5599,7 +5599,7 @@
         <v>16.3</v>
       </c>
       <c r="D323" t="n">
-        <v>2324.87259249454</v>
+        <v>2349.52008294037</v>
       </c>
     </row>
     <row r="324">
@@ -5609,13 +5609,13 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="C324" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="D324" t="n">
-        <v>1597.458468462506</v>
+        <v>1571.151466506137</v>
       </c>
     </row>
     <row r="325">
@@ -5625,13 +5625,13 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C325" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="D325" t="n">
-        <v>1640.247534582037</v>
+        <v>1614.39416741915</v>
       </c>
     </row>
     <row r="326">
@@ -5641,13 +5641,13 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="C326" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="D326" t="n">
-        <v>2082.401217817195</v>
+        <v>2046.821176549279</v>
       </c>
     </row>
     <row r="327">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="C327" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="D327" t="n">
-        <v>2709.974187570322</v>
+        <v>2724.290157519815</v>
       </c>
     </row>
     <row r="328">
@@ -5673,13 +5673,13 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="C328" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="D328" t="n">
-        <v>2139.45330597657</v>
+        <v>2205.37774656366</v>
       </c>
     </row>
     <row r="329">
@@ -5689,13 +5689,13 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="C329" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="D329" t="n">
-        <v>2324.87259249454</v>
+        <v>2320.691615665028</v>
       </c>
     </row>
     <row r="330">
@@ -5705,13 +5705,13 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C330" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="D330" t="n">
-        <v>2695.711165530478</v>
+        <v>2709.875923882144</v>
       </c>
     </row>
     <row r="331">
@@ -5721,13 +5721,13 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="C331" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="D331" t="n">
-        <v>2752.763253689854</v>
+        <v>2753.118624795157</v>
       </c>
     </row>
     <row r="332">
@@ -5737,13 +5737,13 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="C332" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="D332" t="n">
-        <v>2695.711165530478</v>
+        <v>2709.875923882144</v>
       </c>
     </row>
     <row r="333">
@@ -5753,13 +5753,13 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="C333" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="D333" t="n">
-        <v>2980.971606327354</v>
+        <v>2969.332129360222</v>
       </c>
     </row>
     <row r="334">
@@ -5769,13 +5769,13 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="C334" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="D334" t="n">
-        <v>3066.549738566417</v>
+        <v>3070.231764823919</v>
       </c>
     </row>
     <row r="335">
@@ -5785,13 +5785,13 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>-1.7</v>
+        <v>-1.4</v>
       </c>
       <c r="C335" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="D335" t="n">
-        <v>3095.075782646104</v>
+        <v>3084.645998461589</v>
       </c>
     </row>
     <row r="336">
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="C336" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D336" t="n">
-        <v>3109.338804685949</v>
+        <v>3113.474465736932</v>
       </c>
     </row>
     <row r="337">
@@ -5817,13 +5817,13 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>-3.3</v>
+        <v>-3.1</v>
       </c>
       <c r="C337" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D337" t="n">
-        <v>3323.284135283606</v>
+        <v>3329.687970301996</v>
       </c>
     </row>
     <row r="338">
@@ -5833,13 +5833,13 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="C338" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D338" t="n">
-        <v>3408.862267522668</v>
+        <v>3459.416073041035</v>
       </c>
     </row>
     <row r="339">
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="C339" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D339" t="n">
-        <v>3337.547157323449</v>
+        <v>3387.34490485268</v>
       </c>
     </row>
     <row r="340">
@@ -5865,13 +5865,13 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="C340" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="D340" t="n">
-        <v>2809.815341849229</v>
+        <v>2781.947092070499</v>
       </c>
     </row>
     <row r="341">
@@ -5881,13 +5881,13 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C341" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="D341" t="n">
-        <v>2738.500231650009</v>
+        <v>2738.704391157486</v>
       </c>
     </row>
     <row r="342">
@@ -5903,7 +5903,7 @@
         <v>20.2</v>
       </c>
       <c r="D342" t="n">
-        <v>2881.130452048448</v>
+        <v>2911.675194809538</v>
       </c>
     </row>
     <row r="343">
@@ -5913,13 +5913,13 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C343" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="D343" t="n">
-        <v>2781.289297769541</v>
+        <v>2796.36132570817</v>
       </c>
     </row>
     <row r="344">
@@ -5929,13 +5929,13 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="C344" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="D344" t="n">
-        <v>2367.661658614071</v>
+        <v>2363.93431657804</v>
       </c>
     </row>
     <row r="345">
@@ -5945,13 +5945,13 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="C345" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="D345" t="n">
-        <v>1996.823085578132</v>
+        <v>1974.750008360924</v>
       </c>
     </row>
     <row r="346">
@@ -5961,13 +5961,13 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="C346" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="D346" t="n">
-        <v>1825.666821100006</v>
+        <v>1801.779204708873</v>
       </c>
     </row>
     <row r="347">
@@ -5977,13 +5977,13 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="C347" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="D347" t="n">
-        <v>2025.34912965782</v>
+        <v>1989.164241998595</v>
       </c>
     </row>
     <row r="348">
@@ -5993,13 +5993,13 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="C348" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="D348" t="n">
-        <v>2053.875173737507</v>
+        <v>2046.821176549279</v>
       </c>
     </row>
     <row r="349">
@@ -6009,13 +6009,13 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="C349" t="n">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="D349" t="n">
-        <v>2339.135614534383</v>
+        <v>2320.691615665028</v>
       </c>
     </row>
     <row r="350">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="C350" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="D350" t="n">
-        <v>2353.398636574227</v>
+        <v>2363.93431657804</v>
       </c>
     </row>
     <row r="351">
@@ -6041,13 +6041,13 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="C351" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="D351" t="n">
-        <v>2196.505394135946</v>
+        <v>2248.620447476673</v>
       </c>
     </row>
     <row r="352">
@@ -6057,13 +6057,13 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="C352" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="D352" t="n">
-        <v>2239.294460255477</v>
+        <v>2335.105849302699</v>
       </c>
     </row>
     <row r="353">
@@ -6073,13 +6073,13 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="C353" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="D353" t="n">
-        <v>2339.135614534383</v>
+        <v>2407.177017491053</v>
       </c>
     </row>
     <row r="354">
@@ -6089,13 +6089,13 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="C354" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="D354" t="n">
-        <v>2267.820504335164</v>
+        <v>2349.52008294037</v>
       </c>
     </row>
     <row r="355">
@@ -6105,13 +6105,13 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="C355" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="D355" t="n">
-        <v>2239.294460255477</v>
+        <v>2248.620447476673</v>
       </c>
     </row>
     <row r="356">
@@ -6127,7 +6127,7 @@
         <v>13.7</v>
       </c>
       <c r="D356" t="n">
-        <v>1954.034019458601</v>
+        <v>1974.750008360924</v>
       </c>
     </row>
     <row r="357">
@@ -6137,13 +6137,13 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="C357" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="D357" t="n">
-        <v>2196.505394135946</v>
+        <v>2176.549279288318</v>
       </c>
     </row>
     <row r="358">
@@ -6153,13 +6153,13 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="C358" t="n">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="D358" t="n">
-        <v>2167.979350056257</v>
+        <v>2118.892344737634</v>
       </c>
     </row>
     <row r="359">
@@ -6169,13 +6169,13 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="C359" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="D359" t="n">
-        <v>1725.8256668211</v>
+        <v>1729.708036520517</v>
       </c>
     </row>
     <row r="360">
@@ -6191,7 +6191,7 @@
         <v>11.3</v>
       </c>
       <c r="D360" t="n">
-        <v>1611.72149050235</v>
+        <v>1628.808401056821</v>
       </c>
     </row>
     <row r="361">
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C361" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="D361" t="n">
-        <v>1854.192865179694</v>
+        <v>1859.436139259557</v>
       </c>
     </row>
     <row r="362">
@@ -6217,13 +6217,13 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="C362" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="D362" t="n">
-        <v>2239.294460255477</v>
+        <v>2234.206213839002</v>
       </c>
     </row>
     <row r="363">
@@ -6233,13 +6233,13 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="C363" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="D363" t="n">
-        <v>1854.192865179694</v>
+        <v>1845.021905621885</v>
       </c>
     </row>
     <row r="364">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="C364" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="D364" t="n">
-        <v>1725.8256668211</v>
+        <v>1729.708036520517</v>
       </c>
     </row>
     <row r="365">
@@ -6265,13 +6265,13 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="C365" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="D365" t="n">
-        <v>1982.560063538288</v>
+        <v>1974.750008360924</v>
       </c>
     </row>
     <row r="366">
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="C366" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="D366" t="n">
-        <v>2153.716328016414</v>
+        <v>2147.720812012976</v>
       </c>
     </row>
   </sheetData>

--- a/data/a_Eingangsdaten/Wärme/Raumwärmebedarf_täglich_23.xlsx
+++ b/data/a_Eingangsdaten/Wärme/Raumwärmebedarf_täglich_23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D366"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>Raumwärmebedarf [GWh]</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Raumwärmebedarf [MWh]</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -457,13 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="C2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1240.882917466411</v>
+        <v>1258.607809847198</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1258607.809847198</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1483.354292143755</v>
+        <v>1507.402376910017</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1507402.376910017</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="C4" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2110.927261896883</v>
+        <v>2136.706281833616</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2136706.281833616</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="C5" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1882.718909259382</v>
+        <v>1858.641765704584</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1858641.765704584</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="C6" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1697.299622741412</v>
+        <v>1697.657045840407</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1697657.045840407</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="C7" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1811.403799060163</v>
+        <v>1800.101867572156</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1800101.867572156</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="C8" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1882.718909259382</v>
+        <v>1873.276740237691</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1873276.740237691</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="C9" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2025.34912965782</v>
+        <v>2004.991511035654</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2004991.511035654</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="D10" t="n">
-        <v>2139.45330597657</v>
+        <v>2136.706281833616</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2136706.281833616</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2282.083526375008</v>
+        <v>2268.421052631579</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2268421.052631579</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +652,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1996.823085578132</v>
+        <v>1975.72156196944</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1975721.56196944</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +671,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1854.192865179694</v>
+        <v>1829.37181663837</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1829371.81663837</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +690,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="C14" t="n">
-        <v>13.1</v>
+        <v>12.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1868.455887219538</v>
+        <v>1873.276740237691</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1873276.740237691</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +709,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="C15" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1982.560063538288</v>
+        <v>1975.72156196944</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1975721.56196944</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +728,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="D16" t="n">
-        <v>2139.45330597657</v>
+        <v>2136.706281833616</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2136706.281833616</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +747,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="D17" t="n">
-        <v>2438.97676881329</v>
+        <v>2444.040747028862</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2444040.747028863</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +766,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="D18" t="n">
-        <v>2709.974187570322</v>
+        <v>2751.375212224109</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2751375.212224109</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +785,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="C19" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="D19" t="n">
-        <v>3023.760672446886</v>
+        <v>3058.709677419355</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3058709.677419355</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +804,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.5</v>
+        <v>-0.8</v>
       </c>
       <c r="C20" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="D20" t="n">
-        <v>3066.549738566417</v>
+        <v>3044.074702886248</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3044074.702886248</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +823,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="C21" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="D21" t="n">
-        <v>3066.549738566417</v>
+        <v>3102.614601018675</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3102614.601018675</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +842,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="C22" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="D22" t="n">
-        <v>3123.601826725792</v>
+        <v>3146.519524617996</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3146519.524617997</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +861,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="C23" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="D23" t="n">
-        <v>2938.182540207823</v>
+        <v>2956.264855687606</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2956264.855687606</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +880,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="D24" t="n">
-        <v>2852.60440796876</v>
+        <v>2853.820033955858</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2853820.033955858</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +899,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C25" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="D25" t="n">
-        <v>2809.815341849229</v>
+        <v>2839.18505942275</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2839185.05942275</v>
       </c>
     </row>
     <row r="26">
@@ -841,13 +918,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="C26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="D26" t="n">
-        <v>2952.445562247667</v>
+        <v>3014.804753820034</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3014804.753820034</v>
       </c>
     </row>
     <row r="27">
@@ -857,13 +937,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="C27" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>3038.02369448673</v>
+        <v>3073.344651952462</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3073344.651952462</v>
       </c>
     </row>
     <row r="28">
@@ -873,13 +956,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C28" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="D28" t="n">
-        <v>2881.130452048448</v>
+        <v>2883.089983022071</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2883089.983022071</v>
       </c>
     </row>
     <row r="29">
@@ -889,13 +975,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="C29" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="D29" t="n">
-        <v>2980.971606327354</v>
+        <v>2985.53480475382</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2985534.804753819</v>
       </c>
     </row>
     <row r="30">
@@ -905,13 +994,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="C30" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="D30" t="n">
-        <v>3023.760672446886</v>
+        <v>3044.074702886248</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3044074.702886248</v>
       </c>
     </row>
     <row r="31">
@@ -921,13 +1013,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="C31" t="n">
-        <v>18.3</v>
+        <v>17.9</v>
       </c>
       <c r="D31" t="n">
-        <v>2610.133033291416</v>
+        <v>2619.660441426146</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2619660.441426146</v>
       </c>
     </row>
     <row r="32">
@@ -937,13 +1032,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="C32" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="D32" t="n">
-        <v>2453.239790853133</v>
+        <v>2473.310696095076</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2473310.696095076</v>
       </c>
     </row>
     <row r="33">
@@ -953,13 +1051,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="C33" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="D33" t="n">
-        <v>2310.609570454696</v>
+        <v>2312.3259762309</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2312325.9762309</v>
       </c>
     </row>
     <row r="34">
@@ -969,13 +1070,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="C34" t="n">
-        <v>16.5</v>
+        <v>15.9</v>
       </c>
       <c r="D34" t="n">
-        <v>2353.398636574227</v>
+        <v>2326.960950764007</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2326960.950764006</v>
       </c>
     </row>
     <row r="35">
@@ -985,13 +1089,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="C35" t="n">
-        <v>14.7</v>
+        <v>14.2</v>
       </c>
       <c r="D35" t="n">
-        <v>2096.664239857039</v>
+        <v>2078.166383701188</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2078166.383701188</v>
       </c>
     </row>
     <row r="36">
@@ -1001,13 +1108,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="C36" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="D36" t="n">
-        <v>2538.817923092196</v>
+        <v>2531.850594227504</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2531850.594227504</v>
       </c>
     </row>
     <row r="37">
@@ -1017,13 +1127,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C37" t="n">
-        <v>20.4</v>
+        <v>19.5</v>
       </c>
       <c r="D37" t="n">
-        <v>2909.656496128135</v>
+        <v>2853.820033955858</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2853820.033955858</v>
       </c>
     </row>
     <row r="38">
@@ -1033,13 +1146,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9</v>
+        <v>-0</v>
       </c>
       <c r="C38" t="n">
-        <v>20.9</v>
+        <v>20</v>
       </c>
       <c r="D38" t="n">
-        <v>2980.971606327354</v>
+        <v>2926.994906621392</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2926994.906621392</v>
       </c>
     </row>
     <row r="39">
@@ -1049,13 +1165,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.8</v>
+        <v>-2.1</v>
       </c>
       <c r="C39" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="D39" t="n">
-        <v>3251.969025084386</v>
+        <v>3234.329371816639</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3234329.371816639</v>
       </c>
     </row>
     <row r="40">
@@ -1065,13 +1184,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.7</v>
+        <v>-2.2</v>
       </c>
       <c r="C40" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="D40" t="n">
-        <v>3237.706003044543</v>
+        <v>3248.964346349745</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3248964.346349745</v>
       </c>
     </row>
     <row r="41">
@@ -1081,13 +1203,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="C41" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="D41" t="n">
-        <v>3152.12787080548</v>
+        <v>3190.424448217318</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3190424.448217317</v>
       </c>
     </row>
     <row r="42">
@@ -1097,13 +1222,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C42" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="D42" t="n">
-        <v>2809.815341849229</v>
+        <v>2839.18505942275</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2839185.05942275</v>
       </c>
     </row>
     <row r="43">
@@ -1113,13 +1241,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="C43" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="D43" t="n">
-        <v>2381.924680653914</v>
+        <v>2414.770797962648</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2414770.797962648</v>
       </c>
     </row>
     <row r="44">
@@ -1129,13 +1260,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="C44" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="D44" t="n">
-        <v>2153.716328016414</v>
+        <v>2180.611205432937</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2180611.205432937</v>
       </c>
     </row>
     <row r="45">
@@ -1145,13 +1279,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="D45" t="n">
-        <v>2282.083526375008</v>
+        <v>2312.3259762309</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2312325.9762309</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1304,10 @@
         <v>17.3</v>
       </c>
       <c r="D46" t="n">
-        <v>2467.502812892978</v>
+        <v>2531.850594227504</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2531850.594227504</v>
       </c>
     </row>
     <row r="47">
@@ -1177,13 +1317,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="C47" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="D47" t="n">
-        <v>2553.08094513204</v>
+        <v>2648.93039049236</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2648930.39049236</v>
       </c>
     </row>
     <row r="48">
@@ -1193,13 +1336,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="C48" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="D48" t="n">
-        <v>2282.083526375008</v>
+        <v>2283.056027164686</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2283056.027164686</v>
       </c>
     </row>
     <row r="49">
@@ -1209,13 +1355,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="C49" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>1611.72149050235</v>
+        <v>1609.847198641766</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1609847.198641766</v>
       </c>
     </row>
     <row r="50">
@@ -1225,13 +1374,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="C50" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="D50" t="n">
-        <v>1668.773578661725</v>
+        <v>1668.387096774194</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1668387.096774194</v>
       </c>
     </row>
     <row r="51">
@@ -1241,13 +1393,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="C51" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="D51" t="n">
-        <v>1982.560063538288</v>
+        <v>1961.086587436333</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1961086.587436333</v>
       </c>
     </row>
     <row r="52">
@@ -1257,13 +1412,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="C52" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D52" t="n">
-        <v>1839.92984313985</v>
+        <v>1873.276740237691</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1873276.740237691</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1437,10 @@
         <v>12.6</v>
       </c>
       <c r="D53" t="n">
-        <v>1797.140777020319</v>
+        <v>1844.006791171477</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1844006.791171477</v>
       </c>
     </row>
     <row r="54">
@@ -1289,13 +1450,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C54" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="D54" t="n">
-        <v>1896.981931299226</v>
+        <v>1917.181663837012</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1917181.663837012</v>
       </c>
     </row>
     <row r="55">
@@ -1305,13 +1469,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="D55" t="n">
-        <v>1896.981931299226</v>
+        <v>1902.546689303905</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1902546.689303905</v>
       </c>
     </row>
     <row r="56">
@@ -1321,13 +1488,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="C56" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2225.031438215633</v>
+        <v>2224.516129032258</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2224516.129032258</v>
       </c>
     </row>
     <row r="57">
@@ -1337,13 +1507,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="C57" t="n">
-        <v>18.7</v>
+        <v>18.2</v>
       </c>
       <c r="D57" t="n">
-        <v>2667.185121450791</v>
+        <v>2663.565365025467</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2663565.365025467</v>
       </c>
     </row>
     <row r="58">
@@ -1353,13 +1526,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="C58" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D58" t="n">
-        <v>3038.02369448673</v>
+        <v>3044.074702886248</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3044074.702886248</v>
       </c>
     </row>
     <row r="59">
@@ -1369,13 +1545,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="C59" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="D59" t="n">
-        <v>3009.497650407042</v>
+        <v>3014.804753820034</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3014804.753820034</v>
       </c>
     </row>
     <row r="60">
@@ -1385,13 +1564,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="C60" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="D60" t="n">
-        <v>2938.182540207823</v>
+        <v>2970.899830220713</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2970899.830220713</v>
       </c>
     </row>
     <row r="61">
@@ -1401,13 +1583,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C61" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="D61" t="n">
-        <v>2838.341385928916</v>
+        <v>2853.820033955858</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2853820.033955858</v>
       </c>
     </row>
     <row r="62">
@@ -1417,13 +1602,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="C62" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="D62" t="n">
-        <v>2638.659077371103</v>
+        <v>2692.835314091681</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2692835.314091681</v>
       </c>
     </row>
     <row r="63">
@@ -1433,13 +1621,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="C63" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="D63" t="n">
-        <v>2695.711165530478</v>
+        <v>2692.835314091681</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2692835.314091681</v>
       </c>
     </row>
     <row r="64">
@@ -1449,13 +1640,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="C64" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="D64" t="n">
-        <v>2567.343967171884</v>
+        <v>2575.755517826825</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2575755.517826825</v>
       </c>
     </row>
     <row r="65">
@@ -1465,13 +1659,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="C65" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="D65" t="n">
-        <v>2638.659077371103</v>
+        <v>2648.93039049236</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2648930.39049236</v>
       </c>
     </row>
     <row r="66">
@@ -1481,13 +1678,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="C66" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="D66" t="n">
-        <v>2695.711165530478</v>
+        <v>2707.470288624788</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2707470.288624788</v>
       </c>
     </row>
     <row r="67">
@@ -1497,13 +1697,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="C67" t="n">
-        <v>18</v>
+        <v>17.6</v>
       </c>
       <c r="D67" t="n">
-        <v>2567.343967171884</v>
+        <v>2575.755517826825</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2575755.517826825</v>
       </c>
     </row>
     <row r="68">
@@ -1513,13 +1716,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="C68" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="D68" t="n">
-        <v>2553.08094513204</v>
+        <v>2546.485568760611</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2546485.568760611</v>
       </c>
     </row>
     <row r="69">
@@ -1529,13 +1735,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="C69" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="D69" t="n">
-        <v>2139.45330597657</v>
+        <v>2151.341256366723</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2151341.256366723</v>
       </c>
     </row>
     <row r="70">
@@ -1545,13 +1754,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="C70" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="D70" t="n">
-        <v>2082.401217817195</v>
+        <v>2165.97623089983</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2165976.23089983</v>
       </c>
     </row>
     <row r="71">
@@ -1561,13 +1773,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="C71" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="D71" t="n">
-        <v>2767.026275729697</v>
+        <v>2795.28013582343</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2795280.13582343</v>
       </c>
     </row>
     <row r="72">
@@ -1577,13 +1792,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C72" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="D72" t="n">
-        <v>2481.765834932821</v>
+        <v>2487.945670628184</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2487945.670628184</v>
       </c>
     </row>
     <row r="73">
@@ -1593,13 +1811,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="C73" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D73" t="n">
-        <v>1369.250115825005</v>
+        <v>1361.052631578948</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1361052.631578947</v>
       </c>
     </row>
     <row r="74">
@@ -1609,13 +1830,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="C74" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="D74" t="n">
-        <v>1868.455887219538</v>
+        <v>1887.911714770798</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1887911.714770798</v>
       </c>
     </row>
     <row r="75">
@@ -1625,13 +1849,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="D75" t="n">
-        <v>2624.396055331259</v>
+        <v>2634.295415959253</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2634295.415959253</v>
       </c>
     </row>
     <row r="76">
@@ -1641,13 +1868,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="C76" t="n">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="D76" t="n">
-        <v>2396.187702693759</v>
+        <v>2385.500848896434</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2385500.848896435</v>
       </c>
     </row>
     <row r="77">
@@ -1657,13 +1887,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="C77" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="D77" t="n">
-        <v>1697.299622741412</v>
+        <v>1668.387096774194</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1668387.096774194</v>
       </c>
     </row>
     <row r="78">
@@ -1673,13 +1906,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="C78" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="D78" t="n">
-        <v>1412.039181944536</v>
+        <v>1404.957555178268</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1404957.555178268</v>
       </c>
     </row>
     <row r="79">
@@ -1689,13 +1925,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="C79" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="D79" t="n">
-        <v>1526.143358263286</v>
+        <v>1522.037351443124</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1522037.351443124</v>
       </c>
     </row>
     <row r="80">
@@ -1705,13 +1944,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C80" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="D80" t="n">
-        <v>1711.562644781256</v>
+        <v>1712.292020373514</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1712292.020373514</v>
       </c>
     </row>
     <row r="81">
@@ -1721,13 +1963,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="C81" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>1611.72149050235</v>
+        <v>1609.847198641766</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1609847.198641766</v>
       </c>
     </row>
     <row r="82">
@@ -1737,13 +1982,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="C82" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>1340.724071745317</v>
+        <v>1346.41765704584</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1346417.65704584</v>
       </c>
     </row>
     <row r="83">
@@ -1753,13 +2001,16 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="C83" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="D83" t="n">
-        <v>1226.619895426567</v>
+        <v>1229.337860780985</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1229337.860780985</v>
       </c>
     </row>
     <row r="84">
@@ -1769,13 +2020,16 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="C84" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="D84" t="n">
-        <v>1340.724071745317</v>
+        <v>1331.782682512733</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1331782.682512733</v>
       </c>
     </row>
     <row r="85">
@@ -1785,13 +2039,16 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="C85" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="D85" t="n">
-        <v>1740.088688860943</v>
+        <v>1741.561969439729</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1741561.969439728</v>
       </c>
     </row>
     <row r="86">
@@ -1801,13 +2058,16 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="C86" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="D86" t="n">
-        <v>1954.034019458601</v>
+        <v>1961.086587436333</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1961086.587436333</v>
       </c>
     </row>
     <row r="87">
@@ -1817,13 +2077,16 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="C87" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="D87" t="n">
-        <v>2524.554901052353</v>
+        <v>2546.485568760611</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2546485.568760611</v>
       </c>
     </row>
     <row r="88">
@@ -1833,13 +2096,16 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="C88" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="D88" t="n">
-        <v>2496.028856972665</v>
+        <v>2473.310696095076</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2473310.696095076</v>
       </c>
     </row>
     <row r="89">
@@ -1849,13 +2115,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="C89" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="D89" t="n">
-        <v>1811.403799060163</v>
+        <v>1785.466893039049</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1785466.893039049</v>
       </c>
     </row>
     <row r="90">
@@ -1865,13 +2134,16 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="C90" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>1340.724071745317</v>
+        <v>1317.147707979627</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1317147.707979626</v>
       </c>
     </row>
     <row r="91">
@@ -1881,13 +2153,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="C91" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="D91" t="n">
-        <v>1554.669402342974</v>
+        <v>1536.672325976231</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1536672.325976231</v>
       </c>
     </row>
     <row r="92">
@@ -1897,13 +2172,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="C92" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="D92" t="n">
-        <v>1811.403799060163</v>
+        <v>1814.736842105263</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1814736.842105263</v>
       </c>
     </row>
     <row r="93">
@@ -1913,13 +2191,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="C93" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="D93" t="n">
-        <v>2210.768416175789</v>
+        <v>2209.881154499151</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2209881.154499151</v>
       </c>
     </row>
     <row r="94">
@@ -1929,13 +2210,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="C94" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="D94" t="n">
-        <v>2581.606989211728</v>
+        <v>2575.755517826825</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2575755.517826825</v>
       </c>
     </row>
     <row r="95">
@@ -1945,13 +2229,16 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="D95" t="n">
-        <v>2681.448143490635</v>
+        <v>2678.200339558574</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2678200.339558574</v>
       </c>
     </row>
     <row r="96">
@@ -1961,13 +2248,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="C96" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="D96" t="n">
-        <v>2538.817923092196</v>
+        <v>2546.485568760611</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2546485.568760611</v>
       </c>
     </row>
     <row r="97">
@@ -1977,13 +2267,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="C97" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="D97" t="n">
-        <v>2239.294460255477</v>
+        <v>2209.881154499151</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2209881.154499151</v>
       </c>
     </row>
     <row r="98">
@@ -1993,13 +2286,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="C98" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="D98" t="n">
-        <v>2082.401217817195</v>
+        <v>2048.896434634974</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2048896.434634974</v>
       </c>
     </row>
     <row r="99">
@@ -2009,13 +2305,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="C99" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="D99" t="n">
-        <v>2068.138195777351</v>
+        <v>2063.531409168082</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2063531.409168082</v>
       </c>
     </row>
     <row r="100">
@@ -2025,13 +2324,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="C100" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="D100" t="n">
-        <v>1939.770997418757</v>
+        <v>1902.546689303905</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1902546.689303905</v>
       </c>
     </row>
     <row r="101">
@@ -2041,13 +2343,16 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="C101" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="D101" t="n">
-        <v>1568.932424382818</v>
+        <v>1536.672325976231</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1536672.325976231</v>
       </c>
     </row>
     <row r="102">
@@ -2057,13 +2362,16 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="D102" t="n">
-        <v>1740.088688860943</v>
+        <v>1726.926994906622</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1726926.994906622</v>
       </c>
     </row>
     <row r="103">
@@ -2073,13 +2381,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="C103" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="D103" t="n">
-        <v>1825.666821100006</v>
+        <v>1829.37181663837</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1829371.81663837</v>
       </c>
     </row>
     <row r="104">
@@ -2089,13 +2400,16 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="C104" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="D104" t="n">
-        <v>1896.981931299226</v>
+        <v>1917.181663837012</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1917181.663837012</v>
       </c>
     </row>
     <row r="105">
@@ -2105,13 +2419,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="C105" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="D105" t="n">
-        <v>1968.297041498445</v>
+        <v>1961.086587436333</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1961086.587436333</v>
       </c>
     </row>
     <row r="106">
@@ -2121,13 +2438,16 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="C106" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="D106" t="n">
-        <v>1896.981931299226</v>
+        <v>1887.911714770798</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1887911.714770798</v>
       </c>
     </row>
     <row r="107">
@@ -2137,13 +2457,16 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="C107" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="D107" t="n">
-        <v>1782.877754980475</v>
+        <v>1770.831918505942</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1770831.918505942</v>
       </c>
     </row>
     <row r="108">
@@ -2153,13 +2476,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C108" t="n">
-        <v>12.3</v>
+        <v>11.7</v>
       </c>
       <c r="D108" t="n">
-        <v>1754.351710900788</v>
+        <v>1712.292020373514</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1712292.020373514</v>
       </c>
     </row>
     <row r="109">
@@ -2169,13 +2495,16 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C109" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="D109" t="n">
-        <v>1725.8256668211</v>
+        <v>1712.292020373514</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1712292.020373514</v>
       </c>
     </row>
     <row r="110">
@@ -2185,13 +2514,16 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="C110" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="D110" t="n">
-        <v>1797.140777020319</v>
+        <v>1770.831918505942</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1770831.918505942</v>
       </c>
     </row>
     <row r="111">
@@ -2201,13 +2533,16 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="C111" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="D111" t="n">
-        <v>1996.823085578132</v>
+        <v>2004.991511035654</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2004991.511035654</v>
       </c>
     </row>
     <row r="112">
@@ -2217,13 +2552,16 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="C112" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D112" t="n">
-        <v>1312.19802766563</v>
+        <v>1317.147707979627</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1317147.707979626</v>
       </c>
     </row>
     <row r="113">
@@ -2233,13 +2571,16 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="C113" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="D113" t="n">
-        <v>912.8334105500032</v>
+        <v>878.0984719864176</v>
+      </c>
+      <c r="E113" t="n">
+        <v>878098.4719864177</v>
       </c>
     </row>
     <row r="114">
@@ -2249,13 +2590,16 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="C114" t="n">
-        <v>7.6</v>
+        <v>7.300000000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>1083.989675028129</v>
+        <v>1068.353140916808</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1068353.140916808</v>
       </c>
     </row>
     <row r="115">
@@ -2265,13 +2609,16 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="C115" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="D115" t="n">
-        <v>1511.880336223443</v>
+        <v>1536.672325976231</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1536672.325976231</v>
       </c>
     </row>
     <row r="116">
@@ -2281,13 +2628,16 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="C116" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="D116" t="n">
-        <v>1968.297041498445</v>
+        <v>1975.72156196944</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1975721.56196944</v>
       </c>
     </row>
     <row r="117">
@@ -2297,13 +2647,16 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="C117" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="D117" t="n">
-        <v>2053.875173737507</v>
+        <v>2048.896434634974</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2048896.434634974</v>
       </c>
     </row>
     <row r="118">
@@ -2313,13 +2666,16 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="C118" t="n">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="D118" t="n">
-        <v>1782.877754980475</v>
+        <v>1741.561969439729</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1741561.969439728</v>
       </c>
     </row>
     <row r="119">
@@ -2329,13 +2685,16 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="D119" t="n">
-        <v>1426.30220398438</v>
+        <v>1404.957555178268</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1404957.555178268</v>
       </c>
     </row>
     <row r="120">
@@ -2345,13 +2704,16 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="C120" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>1326.461049705473</v>
+        <v>1317.147707979627</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1317147.707979626</v>
       </c>
     </row>
     <row r="121">
@@ -2361,13 +2723,16 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="C121" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="D121" t="n">
-        <v>1454.828248064068</v>
+        <v>1448.862478777589</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1448862.478777589</v>
       </c>
     </row>
     <row r="122">
@@ -2377,12 +2742,15 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2393,12 +2761,15 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2409,12 +2780,15 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2425,12 +2799,15 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2441,12 +2818,15 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2457,12 +2837,15 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2473,12 +2856,15 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2489,12 +2875,15 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>12.5</v>
+        <v>13.1</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2505,12 +2894,15 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2521,12 +2913,15 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2537,12 +2932,15 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2553,12 +2951,15 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2569,12 +2970,15 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2585,12 +2989,15 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2601,12 +3008,15 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2617,12 +3027,15 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2633,12 +3046,15 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2649,12 +3065,15 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2665,12 +3084,15 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2681,12 +3103,15 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2697,12 +3122,15 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2713,12 +3141,15 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2729,12 +3160,15 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2745,12 +3179,15 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2761,12 +3198,15 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2777,12 +3217,15 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
       <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2793,12 +3236,15 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2809,12 +3255,15 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2825,12 +3274,15 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2841,12 +3293,15 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2857,12 +3312,15 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2873,12 +3331,15 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
       </c>
       <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2889,12 +3350,15 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2905,12 +3369,15 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2921,12 +3388,15 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2937,12 +3407,15 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
       </c>
       <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2953,12 +3426,15 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>16.3</v>
+        <v>16.9</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2969,12 +3445,15 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2985,12 +3464,15 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3001,12 +3483,15 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3017,12 +3502,15 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3033,12 +3521,15 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>19.7</v>
+        <v>20.3</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3049,12 +3540,15 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>19.1</v>
+        <v>19.8</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
       </c>
       <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3065,12 +3559,15 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>17.5</v>
+        <v>18.1</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3081,12 +3578,15 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3097,12 +3597,15 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3113,12 +3616,15 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>16.6</v>
+        <v>17.2</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
       <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3129,12 +3635,15 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
       </c>
       <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3145,12 +3654,15 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>20.1</v>
+        <v>20.6</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3161,12 +3673,15 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
       <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3177,12 +3692,15 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
       </c>
       <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3193,12 +3711,15 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
       </c>
       <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3209,12 +3730,15 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3225,12 +3749,15 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
       </c>
       <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3241,12 +3768,15 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
       </c>
       <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3257,12 +3787,15 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>21</v>
+        <v>21.6</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
       </c>
       <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3273,12 +3806,15 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
       </c>
       <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3289,12 +3825,15 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3305,12 +3844,15 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
       </c>
       <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3321,12 +3863,15 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3337,12 +3882,15 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
       </c>
       <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3353,12 +3901,15 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3369,12 +3920,15 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3385,12 +3939,15 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3401,12 +3958,15 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3417,12 +3977,15 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3433,12 +3996,15 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3449,12 +4015,15 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3465,12 +4034,15 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3481,12 +4053,15 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3497,12 +4072,15 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3513,12 +4091,15 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
       </c>
       <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3537,6 +4118,9 @@
       <c r="D194" t="n">
         <v>0</v>
       </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -3553,6 +4137,9 @@
       <c r="D195" t="n">
         <v>0</v>
       </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -3561,12 +4148,15 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3585,6 +4175,9 @@
       <c r="D197" t="n">
         <v>0</v>
       </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -3601,6 +4194,9 @@
       <c r="D198" t="n">
         <v>0</v>
       </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -3609,12 +4205,15 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
       </c>
       <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3625,12 +4224,15 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
       </c>
       <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3641,12 +4243,15 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3657,12 +4262,15 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3673,12 +4281,15 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>16</v>
+        <v>16.3</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3689,12 +4300,15 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3713,6 +4327,9 @@
       <c r="D205" t="n">
         <v>0</v>
       </c>
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -3721,12 +4338,15 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
       </c>
       <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3737,12 +4357,15 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3753,12 +4376,15 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3769,12 +4395,15 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3785,12 +4414,15 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
       </c>
       <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3801,12 +4433,15 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
       </c>
       <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3817,12 +4452,15 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
       </c>
       <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3833,12 +4471,15 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
       </c>
       <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3849,12 +4490,15 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>16.5</v>
+        <v>16.9</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3865,12 +4509,15 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3889,6 +4536,9 @@
       <c r="D216" t="n">
         <v>0</v>
       </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -3897,12 +4547,15 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
       </c>
       <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3913,12 +4566,15 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
       </c>
       <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3929,12 +4585,15 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
       </c>
       <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3945,12 +4604,15 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
       </c>
       <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3961,12 +4623,15 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3977,12 +4642,15 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3993,12 +4661,15 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
       </c>
       <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4009,12 +4680,15 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4025,12 +4699,15 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4049,6 +4726,9 @@
       <c r="D226" t="n">
         <v>0</v>
       </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -4057,12 +4737,15 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4081,6 +4764,9 @@
       <c r="D228" t="n">
         <v>0</v>
       </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -4089,12 +4775,15 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4105,12 +4794,15 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4121,12 +4813,15 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4137,12 +4832,15 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4153,12 +4851,15 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4169,12 +4870,15 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
       </c>
       <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4185,12 +4889,15 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
       </c>
       <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4201,12 +4908,15 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4217,12 +4927,15 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4241,6 +4954,9 @@
       <c r="D238" t="n">
         <v>0</v>
       </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -4257,6 +4973,9 @@
       <c r="D239" t="n">
         <v>0</v>
       </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -4273,6 +4992,9 @@
       <c r="D240" t="n">
         <v>0</v>
       </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -4281,12 +5003,15 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="C241" t="n">
         <v>0</v>
       </c>
       <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4297,12 +5022,15 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
       </c>
       <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4313,12 +5041,15 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
       </c>
       <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4329,12 +5060,15 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
       </c>
       <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4345,12 +5079,15 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="C245" t="n">
         <v>0</v>
       </c>
       <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4361,12 +5098,15 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="C246" t="n">
         <v>0</v>
       </c>
       <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4377,12 +5117,15 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="C247" t="n">
         <v>0</v>
       </c>
       <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4393,12 +5136,15 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
       </c>
       <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4409,12 +5155,15 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
       <c r="C249" t="n">
         <v>0</v>
       </c>
       <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4425,12 +5174,15 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="C250" t="n">
         <v>0</v>
       </c>
       <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4441,12 +5193,15 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="C251" t="n">
         <v>0</v>
       </c>
       <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4457,12 +5212,15 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="C252" t="n">
         <v>0</v>
       </c>
       <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4473,12 +5231,15 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
       </c>
       <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4489,12 +5250,15 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
       </c>
       <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4505,12 +5269,15 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
       </c>
       <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4521,12 +5288,15 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
       </c>
       <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4537,12 +5307,15 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
       </c>
       <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4553,12 +5326,15 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="C258" t="n">
         <v>0</v>
       </c>
       <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4569,12 +5345,15 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="C259" t="n">
         <v>0</v>
       </c>
       <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4585,12 +5364,15 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
       </c>
       <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4601,12 +5383,15 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
       </c>
       <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4617,12 +5402,15 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="C262" t="n">
         <v>0</v>
       </c>
       <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4633,12 +5421,15 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="C263" t="n">
         <v>0</v>
       </c>
       <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4649,12 +5440,15 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="C264" t="n">
         <v>0</v>
       </c>
       <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4665,12 +5459,15 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="C265" t="n">
         <v>0</v>
       </c>
       <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4681,12 +5478,15 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="C266" t="n">
         <v>0</v>
       </c>
       <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4697,12 +5497,15 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="C267" t="n">
         <v>0</v>
       </c>
       <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4713,12 +5516,15 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
       </c>
       <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4729,12 +5535,15 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
       </c>
       <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4745,12 +5554,15 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="C270" t="n">
         <v>0</v>
       </c>
       <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4769,6 +5581,9 @@
       <c r="D271" t="n">
         <v>0</v>
       </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -4777,12 +5592,15 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
       </c>
       <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4793,12 +5611,15 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
       </c>
       <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4809,12 +5630,15 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="C274" t="n">
         <v>0</v>
       </c>
       <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4825,13 +5649,16 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="C275" t="n">
-        <v>5.300000000000001</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="D275" t="n">
-        <v>755.9401681117215</v>
+        <v>761.0186757215619</v>
+      </c>
+      <c r="E275" t="n">
+        <v>761018.6757215619</v>
       </c>
     </row>
     <row r="276">
@@ -4849,6 +5676,9 @@
       <c r="D276" t="n">
         <v>0</v>
       </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -4865,6 +5695,9 @@
       <c r="D277" t="n">
         <v>0</v>
       </c>
+      <c r="E277" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -4873,13 +5706,16 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="C278" t="n">
-        <v>7.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D278" t="n">
-        <v>1098.252697067973</v>
+        <v>1082.988115449915</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1082988.115449915</v>
       </c>
     </row>
     <row r="279">
@@ -4889,13 +5725,16 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="C279" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D279" t="n">
-        <v>1169.567807267191</v>
+        <v>1170.797962648557</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1170797.962648557</v>
       </c>
     </row>
     <row r="280">
@@ -4905,13 +5744,16 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="C280" t="n">
-        <v>7.300000000000001</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="D280" t="n">
-        <v>1041.200608908598</v>
+        <v>1053.718166383701</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1053718.166383701</v>
       </c>
     </row>
     <row r="281">
@@ -4921,13 +5763,16 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="C281" t="n">
-        <v>5.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="D281" t="n">
-        <v>827.2552783109405</v>
+        <v>863.4634974533108</v>
+      </c>
+      <c r="E281" t="n">
+        <v>863463.4974533108</v>
       </c>
     </row>
     <row r="282">
@@ -4937,13 +5782,16 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="C282" t="n">
-        <v>6.6</v>
+        <v>6.300000000000001</v>
       </c>
       <c r="D282" t="n">
-        <v>941.3594546296908</v>
+        <v>922.0033955857386</v>
+      </c>
+      <c r="E282" t="n">
+        <v>922003.3955857386</v>
       </c>
     </row>
     <row r="283">
@@ -4953,13 +5801,16 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="C283" t="n">
-        <v>6.300000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="D283" t="n">
-        <v>898.5703885101595</v>
+        <v>863.4634974533108</v>
+      </c>
+      <c r="E283" t="n">
+        <v>863463.4974533108</v>
       </c>
     </row>
     <row r="284">
@@ -4969,12 +5820,15 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>15.1</v>
+        <v>15.4</v>
       </c>
       <c r="C284" t="n">
         <v>0</v>
       </c>
       <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4985,12 +5839,15 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="C285" t="n">
         <v>0</v>
       </c>
       <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5001,13 +5858,16 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="C286" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>713.1511019921901</v>
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -5017,12 +5877,15 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
       </c>
       <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5039,7 +5902,10 @@
         <v>7.1</v>
       </c>
       <c r="D288" t="n">
-        <v>1012.67456482891</v>
+        <v>1039.083191850594</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1039083.191850594</v>
       </c>
     </row>
     <row r="289">
@@ -5049,13 +5915,16 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="C289" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="D289" t="n">
-        <v>1911.244953339069</v>
+        <v>1917.181663837012</v>
+      </c>
+      <c r="E289" t="n">
+        <v>1917181.663837012</v>
       </c>
     </row>
     <row r="290">
@@ -5065,13 +5934,16 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="C290" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="D290" t="n">
-        <v>2096.664239857039</v>
+        <v>2092.801358234296</v>
+      </c>
+      <c r="E290" t="n">
+        <v>2092801.358234296</v>
       </c>
     </row>
     <row r="291">
@@ -5081,13 +5953,16 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="C291" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="D291" t="n">
-        <v>2039.612151697664</v>
+        <v>2063.531409168082</v>
+      </c>
+      <c r="E291" t="n">
+        <v>2063531.409168082</v>
       </c>
     </row>
     <row r="292">
@@ -5097,13 +5972,16 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="C292" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="D292" t="n">
-        <v>1868.455887219538</v>
+        <v>1887.911714770798</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1887911.714770798</v>
       </c>
     </row>
     <row r="293">
@@ -5113,13 +5991,16 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="C293" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D293" t="n">
-        <v>1383.513137864849</v>
+        <v>1361.052631578948</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1361052.631578947</v>
       </c>
     </row>
     <row r="294">
@@ -5129,13 +6010,16 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="C294" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D294" t="n">
-        <v>1340.724071745317</v>
+        <v>1346.41765704584</v>
+      </c>
+      <c r="E294" t="n">
+        <v>1346417.65704584</v>
       </c>
     </row>
     <row r="295">
@@ -5145,13 +6029,16 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="C295" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="D295" t="n">
-        <v>1183.830829307035</v>
+        <v>1185.432937181664</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1185432.937181664</v>
       </c>
     </row>
     <row r="296">
@@ -5161,13 +6048,16 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="C296" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D296" t="n">
-        <v>1326.461049705473</v>
+        <v>1331.782682512733</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1331782.682512733</v>
       </c>
     </row>
     <row r="297">
@@ -5177,13 +6067,16 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="C297" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="D297" t="n">
-        <v>1454.828248064068</v>
+        <v>1463.497453310696</v>
+      </c>
+      <c r="E297" t="n">
+        <v>1463497.453310696</v>
       </c>
     </row>
     <row r="298">
@@ -5193,13 +6086,16 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="C298" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D298" t="n">
-        <v>1340.724071745317</v>
+        <v>1361.052631578948</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1361052.631578947</v>
       </c>
     </row>
     <row r="299">
@@ -5209,13 +6105,16 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="C299" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D299" t="n">
-        <v>1440.565226024224</v>
+        <v>1463.497453310696</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1463497.453310696</v>
       </c>
     </row>
     <row r="300">
@@ -5225,13 +6124,16 @@
         </is>
       </c>
       <c r="B300" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C300" t="n">
         <v>9.9</v>
       </c>
-      <c r="C300" t="n">
-        <v>10.1</v>
-      </c>
       <c r="D300" t="n">
-        <v>1440.565226024224</v>
+        <v>1448.862478777589</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1448862.478777589</v>
       </c>
     </row>
     <row r="301">
@@ -5241,13 +6143,16 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C301" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="D301" t="n">
-        <v>1568.932424382818</v>
+        <v>1565.942275042445</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1565942.275042445</v>
       </c>
     </row>
     <row r="302">
@@ -5257,13 +6162,16 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="C302" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="D302" t="n">
-        <v>1483.354292143755</v>
+        <v>1463.497453310696</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1463497.453310696</v>
       </c>
     </row>
     <row r="303">
@@ -5273,13 +6181,16 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="C303" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="D303" t="n">
-        <v>1198.093851346879</v>
+        <v>1185.432937181664</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1185432.937181664</v>
       </c>
     </row>
     <row r="304">
@@ -5289,13 +6200,16 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="C304" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D304" t="n">
-        <v>1212.356873386723</v>
+        <v>1214.702886247878</v>
+      </c>
+      <c r="E304" t="n">
+        <v>1214702.886247878</v>
       </c>
     </row>
     <row r="305">
@@ -5305,13 +6219,16 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C305" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D305" t="n">
-        <v>1469.091270103912</v>
+        <v>1492.76740237691</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1492767.40237691</v>
       </c>
     </row>
     <row r="306">
@@ -5321,13 +6238,16 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="C306" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="D306" t="n">
-        <v>1454.828248064068</v>
+        <v>1448.862478777589</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1448862.478777589</v>
       </c>
     </row>
     <row r="307">
@@ -5337,13 +6257,16 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="C307" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="D307" t="n">
-        <v>1540.406380303131</v>
+        <v>1522.037351443124</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1522037.351443124</v>
       </c>
     </row>
     <row r="308">
@@ -5353,13 +6276,16 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="C308" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="D308" t="n">
-        <v>1825.666821100006</v>
+        <v>1814.736842105263</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1814736.842105263</v>
       </c>
     </row>
     <row r="309">
@@ -5369,13 +6295,16 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="C309" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="D309" t="n">
-        <v>1839.92984313985</v>
+        <v>1829.37181663837</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1829371.81663837</v>
       </c>
     </row>
     <row r="310">
@@ -5385,13 +6314,16 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="C310" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="D310" t="n">
-        <v>1554.669402342974</v>
+        <v>1551.307300509338</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1551307.300509338</v>
       </c>
     </row>
     <row r="311">
@@ -5401,13 +6333,16 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C311" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="D311" t="n">
-        <v>1554.669402342974</v>
+        <v>1565.942275042445</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1565942.275042445</v>
       </c>
     </row>
     <row r="312">
@@ -5417,13 +6352,16 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="C312" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="D312" t="n">
-        <v>1740.088688860943</v>
+        <v>1756.196943972835</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1756196.943972835</v>
       </c>
     </row>
     <row r="313">
@@ -5433,13 +6371,16 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="C313" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="D313" t="n">
-        <v>1839.92984313985</v>
+        <v>1844.006791171477</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1844006.791171477</v>
       </c>
     </row>
     <row r="314">
@@ -5449,13 +6390,16 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="C314" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="D314" t="n">
-        <v>1839.92984313985</v>
+        <v>1844.006791171477</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1844006.791171477</v>
       </c>
     </row>
     <row r="315">
@@ -5465,13 +6409,16 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="C315" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="D315" t="n">
-        <v>1925.507975378913</v>
+        <v>1917.181663837012</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1917181.663837012</v>
       </c>
     </row>
     <row r="316">
@@ -5481,13 +6428,16 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="C316" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="D316" t="n">
-        <v>2125.190283936726</v>
+        <v>2122.071307300509</v>
+      </c>
+      <c r="E316" t="n">
+        <v>2122071.307300509</v>
       </c>
     </row>
     <row r="317">
@@ -5497,13 +6447,16 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="C317" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="D317" t="n">
-        <v>2196.505394135946</v>
+        <v>2209.881154499151</v>
+      </c>
+      <c r="E317" t="n">
+        <v>2209881.154499151</v>
       </c>
     </row>
     <row r="318">
@@ -5513,13 +6466,16 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="C318" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="D318" t="n">
-        <v>1754.351710900788</v>
+        <v>1756.196943972835</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1756196.943972835</v>
       </c>
     </row>
     <row r="319">
@@ -5529,13 +6485,16 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="C319" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="D319" t="n">
-        <v>1469.091270103912</v>
+        <v>1463.497453310696</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1463497.453310696</v>
       </c>
     </row>
     <row r="320">
@@ -5545,13 +6504,16 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C320" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="D320" t="n">
-        <v>1725.8256668211</v>
+        <v>1712.292020373514</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1712292.020373514</v>
       </c>
     </row>
     <row r="321">
@@ -5561,13 +6523,16 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="C321" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="D321" t="n">
-        <v>2025.34912965782</v>
+        <v>2034.261460101868</v>
+      </c>
+      <c r="E321" t="n">
+        <v>2034261.460101868</v>
       </c>
     </row>
     <row r="322">
@@ -5577,13 +6542,16 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="C322" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="D322" t="n">
-        <v>2310.609570454696</v>
+        <v>2326.960950764007</v>
+      </c>
+      <c r="E322" t="n">
+        <v>2326960.950764006</v>
       </c>
     </row>
     <row r="323">
@@ -5593,13 +6561,16 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C323" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="D323" t="n">
-        <v>2324.87259249454</v>
+        <v>2341.595925297114</v>
+      </c>
+      <c r="E323" t="n">
+        <v>2341595.925297114</v>
       </c>
     </row>
     <row r="324">
@@ -5609,13 +6580,16 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="C324" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D324" t="n">
-        <v>1597.458468462506</v>
+        <v>1551.307300509338</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1551307.300509338</v>
       </c>
     </row>
     <row r="325">
@@ -5625,13 +6599,16 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="C325" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="D325" t="n">
-        <v>1640.247534582037</v>
+        <v>1609.847198641766</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1609847.198641766</v>
       </c>
     </row>
     <row r="326">
@@ -5641,13 +6618,16 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="C326" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="D326" t="n">
-        <v>2082.401217817195</v>
+        <v>2063.531409168082</v>
+      </c>
+      <c r="E326" t="n">
+        <v>2063531.409168082</v>
       </c>
     </row>
     <row r="327">
@@ -5657,13 +6637,16 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C327" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="D327" t="n">
-        <v>2709.974187570322</v>
+        <v>2707.470288624788</v>
+      </c>
+      <c r="E327" t="n">
+        <v>2707470.288624788</v>
       </c>
     </row>
     <row r="328">
@@ -5673,13 +6656,16 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="C328" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="D328" t="n">
-        <v>2139.45330597657</v>
+        <v>2151.341256366723</v>
+      </c>
+      <c r="E328" t="n">
+        <v>2151341.256366723</v>
       </c>
     </row>
     <row r="329">
@@ -5689,13 +6675,16 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="C329" t="n">
-        <v>16.3</v>
+        <v>16</v>
       </c>
       <c r="D329" t="n">
-        <v>2324.87259249454</v>
+        <v>2341.595925297114</v>
+      </c>
+      <c r="E329" t="n">
+        <v>2341595.925297114</v>
       </c>
     </row>
     <row r="330">
@@ -5705,13 +6694,16 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="C330" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="D330" t="n">
-        <v>2695.711165530478</v>
+        <v>2692.835314091681</v>
+      </c>
+      <c r="E330" t="n">
+        <v>2692835.314091681</v>
       </c>
     </row>
     <row r="331">
@@ -5721,13 +6713,16 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="C331" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="D331" t="n">
-        <v>2752.763253689854</v>
+        <v>2736.740237691002</v>
+      </c>
+      <c r="E331" t="n">
+        <v>2736740.237691002</v>
       </c>
     </row>
     <row r="332">
@@ -5737,13 +6732,16 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="C332" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="D332" t="n">
-        <v>2695.711165530478</v>
+        <v>2722.105263157895</v>
+      </c>
+      <c r="E332" t="n">
+        <v>2722105.263157895</v>
       </c>
     </row>
     <row r="333">
@@ -5753,13 +6751,16 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="C333" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="D333" t="n">
-        <v>2980.971606327354</v>
+        <v>2985.53480475382</v>
+      </c>
+      <c r="E333" t="n">
+        <v>2985534.804753819</v>
       </c>
     </row>
     <row r="334">
@@ -5769,13 +6770,16 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>-1.5</v>
+        <v>-0.9</v>
       </c>
       <c r="C334" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="D334" t="n">
-        <v>3066.549738566417</v>
+        <v>3058.709677419355</v>
+      </c>
+      <c r="E334" t="n">
+        <v>3058709.677419355</v>
       </c>
     </row>
     <row r="335">
@@ -5785,13 +6789,16 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="C335" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D335" t="n">
-        <v>3095.075782646104</v>
+        <v>3146.519524617996</v>
+      </c>
+      <c r="E335" t="n">
+        <v>3146519.524617997</v>
       </c>
     </row>
     <row r="336">
@@ -5801,13 +6808,16 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="C336" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D336" t="n">
-        <v>3109.338804685949</v>
+        <v>3161.154499151104</v>
+      </c>
+      <c r="E336" t="n">
+        <v>3161154.499151104</v>
       </c>
     </row>
     <row r="337">
@@ -5817,13 +6827,16 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>-3.3</v>
+        <v>-2.8</v>
       </c>
       <c r="C337" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="D337" t="n">
-        <v>3323.284135283606</v>
+        <v>3336.774193548387</v>
+      </c>
+      <c r="E337" t="n">
+        <v>3336774.193548387</v>
       </c>
     </row>
     <row r="338">
@@ -5833,13 +6846,16 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>-3.9</v>
+        <v>-3.6</v>
       </c>
       <c r="C338" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="D338" t="n">
-        <v>3408.862267522668</v>
+        <v>3453.853989813243</v>
+      </c>
+      <c r="E338" t="n">
+        <v>3453853.989813243</v>
       </c>
     </row>
     <row r="339">
@@ -5849,13 +6865,16 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>-3.4</v>
+        <v>-2.9</v>
       </c>
       <c r="C339" t="n">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="D339" t="n">
-        <v>3337.547157323449</v>
+        <v>3351.409168081494</v>
+      </c>
+      <c r="E339" t="n">
+        <v>3351409.168081494</v>
       </c>
     </row>
     <row r="340">
@@ -5865,13 +6884,16 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C340" t="n">
-        <v>19.7</v>
+        <v>19.2</v>
       </c>
       <c r="D340" t="n">
-        <v>2809.815341849229</v>
+        <v>2809.915110356536</v>
+      </c>
+      <c r="E340" t="n">
+        <v>2809915.110356536</v>
       </c>
     </row>
     <row r="341">
@@ -5881,13 +6903,16 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="C341" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="D341" t="n">
-        <v>2738.500231650009</v>
+        <v>2751.375212224109</v>
+      </c>
+      <c r="E341" t="n">
+        <v>2751375.212224109</v>
       </c>
     </row>
     <row r="342">
@@ -5897,13 +6922,16 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C342" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="D342" t="n">
-        <v>2881.130452048448</v>
+        <v>2912.359932088285</v>
+      </c>
+      <c r="E342" t="n">
+        <v>2912359.932088285</v>
       </c>
     </row>
     <row r="343">
@@ -5913,13 +6941,16 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C343" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="D343" t="n">
-        <v>2781.289297769541</v>
+        <v>2809.915110356536</v>
+      </c>
+      <c r="E343" t="n">
+        <v>2809915.110356536</v>
       </c>
     </row>
     <row r="344">
@@ -5929,13 +6960,16 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="C344" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="D344" t="n">
-        <v>2367.661658614071</v>
+        <v>2341.595925297114</v>
+      </c>
+      <c r="E344" t="n">
+        <v>2341595.925297114</v>
       </c>
     </row>
     <row r="345">
@@ -5945,13 +6979,16 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="C345" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="D345" t="n">
-        <v>1996.823085578132</v>
+        <v>1975.72156196944</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1975721.56196944</v>
       </c>
     </row>
     <row r="346">
@@ -5961,13 +6998,16 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="C346" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="D346" t="n">
-        <v>1825.666821100006</v>
+        <v>1814.736842105263</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1814736.842105263</v>
       </c>
     </row>
     <row r="347">
@@ -5977,13 +7017,16 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="C347" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="D347" t="n">
-        <v>2025.34912965782</v>
+        <v>2004.991511035654</v>
+      </c>
+      <c r="E347" t="n">
+        <v>2004991.511035654</v>
       </c>
     </row>
     <row r="348">
@@ -5993,13 +7036,16 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="C348" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="D348" t="n">
-        <v>2053.875173737507</v>
+        <v>2078.166383701188</v>
+      </c>
+      <c r="E348" t="n">
+        <v>2078166.383701188</v>
       </c>
     </row>
     <row r="349">
@@ -6009,13 +7055,16 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="C349" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="D349" t="n">
-        <v>2339.135614534383</v>
+        <v>2341.595925297114</v>
+      </c>
+      <c r="E349" t="n">
+        <v>2341595.925297114</v>
       </c>
     </row>
     <row r="350">
@@ -6025,13 +7074,16 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C350" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="D350" t="n">
-        <v>2353.398636574227</v>
+        <v>2341.595925297114</v>
+      </c>
+      <c r="E350" t="n">
+        <v>2341595.925297114</v>
       </c>
     </row>
     <row r="351">
@@ -6041,13 +7093,16 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="C351" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="D351" t="n">
-        <v>2196.505394135946</v>
+        <v>2209.881154499151</v>
+      </c>
+      <c r="E351" t="n">
+        <v>2209881.154499151</v>
       </c>
     </row>
     <row r="352">
@@ -6063,7 +7118,10 @@
         <v>15.7</v>
       </c>
       <c r="D352" t="n">
-        <v>2239.294460255477</v>
+        <v>2297.691001697793</v>
+      </c>
+      <c r="E352" t="n">
+        <v>2297691.001697793</v>
       </c>
     </row>
     <row r="353">
@@ -6073,13 +7131,16 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C353" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="D353" t="n">
-        <v>2339.135614534383</v>
+        <v>2370.865874363328</v>
+      </c>
+      <c r="E353" t="n">
+        <v>2370865.874363328</v>
       </c>
     </row>
     <row r="354">
@@ -6095,7 +7156,10 @@
         <v>15.9</v>
       </c>
       <c r="D354" t="n">
-        <v>2267.820504335164</v>
+        <v>2326.960950764007</v>
+      </c>
+      <c r="E354" t="n">
+        <v>2326960.950764006</v>
       </c>
     </row>
     <row r="355">
@@ -6105,13 +7169,16 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="C355" t="n">
-        <v>15.7</v>
+        <v>15.3</v>
       </c>
       <c r="D355" t="n">
-        <v>2239.294460255477</v>
+        <v>2239.151103565365</v>
+      </c>
+      <c r="E355" t="n">
+        <v>2239151.103565365</v>
       </c>
     </row>
     <row r="356">
@@ -6121,13 +7188,16 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="C356" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="D356" t="n">
-        <v>1954.034019458601</v>
+        <v>1946.451612903226</v>
+      </c>
+      <c r="E356" t="n">
+        <v>1946451.612903226</v>
       </c>
     </row>
     <row r="357">
@@ -6137,13 +7207,16 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="C357" t="n">
-        <v>15.4</v>
+        <v>14.9</v>
       </c>
       <c r="D357" t="n">
-        <v>2196.505394135946</v>
+        <v>2180.611205432937</v>
+      </c>
+      <c r="E357" t="n">
+        <v>2180611.205432937</v>
       </c>
     </row>
     <row r="358">
@@ -6153,13 +7226,16 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="C358" t="n">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="D358" t="n">
-        <v>2167.979350056257</v>
+        <v>2151.341256366723</v>
+      </c>
+      <c r="E358" t="n">
+        <v>2151341.256366723</v>
       </c>
     </row>
     <row r="359">
@@ -6169,13 +7245,16 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C359" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="D359" t="n">
-        <v>1725.8256668211</v>
+        <v>1712.292020373514</v>
+      </c>
+      <c r="E359" t="n">
+        <v>1712292.020373514</v>
       </c>
     </row>
     <row r="360">
@@ -6185,13 +7264,16 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="C360" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="D360" t="n">
-        <v>1611.72149050235</v>
+        <v>1624.482173174873</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1624482.173174873</v>
       </c>
     </row>
     <row r="361">
@@ -6201,13 +7283,16 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="C361" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="D361" t="n">
-        <v>1854.192865179694</v>
+        <v>1873.276740237691</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1873276.740237691</v>
       </c>
     </row>
     <row r="362">
@@ -6217,13 +7302,16 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="C362" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="D362" t="n">
-        <v>2239.294460255477</v>
+        <v>2253.786078098472</v>
+      </c>
+      <c r="E362" t="n">
+        <v>2253786.078098472</v>
       </c>
     </row>
     <row r="363">
@@ -6233,13 +7321,16 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="C363" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="D363" t="n">
-        <v>1854.192865179694</v>
+        <v>1844.006791171477</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1844006.791171477</v>
       </c>
     </row>
     <row r="364">
@@ -6249,13 +7340,16 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C364" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="D364" t="n">
-        <v>1725.8256668211</v>
+        <v>1726.926994906622</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1726926.994906622</v>
       </c>
     </row>
     <row r="365">
@@ -6265,13 +7359,16 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="C365" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="D365" t="n">
-        <v>1982.560063538288</v>
+        <v>1990.356536502547</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1990356.536502547</v>
       </c>
     </row>
     <row r="366">
@@ -6281,13 +7378,16 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="C366" t="n">
-        <v>15.1</v>
+        <v>14.6</v>
       </c>
       <c r="D366" t="n">
-        <v>2153.716328016414</v>
+        <v>2136.706281833616</v>
+      </c>
+      <c r="E366" t="n">
+        <v>2136706.281833616</v>
       </c>
     </row>
   </sheetData>
